--- a/projects/psmmc-dashboard/tests/fixtures/withdrawals-xss.xlsx
+++ b/projects/psmmc-dashboard/tests/fixtures/withdrawals-xss.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -459,9 +459,49 @@
         <v>XSS probe</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>5999999000000</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="D4" t="str">
+        <v>DISPATCHED</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TAB</v>
+      </c>
+      <c r="F4" t="str">
+        <v>=HYPERLINK("http://evil.example","pwn")</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>5999999000000</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="D5" t="str">
+        <v>DISPATCHED</v>
+      </c>
+      <c r="E5" t="str">
+        <v>TAB</v>
+      </c>
+      <c r="F5" t="str">
+        <v>=HYPERLINK("http://evil.example","pwn")</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>